--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>300</v>
+        <v>5</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
         <v>10</v>
       </c>
       <c r="K16" s="15">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.461538461538</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="M16" s="15">
-        <v>-11.111111111111</v>
+        <v>5</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.885245901639</v>
+        <v>-84.558823529411</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
         <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="I17" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J17" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K17" s="15">
-        <v>33.333333333333</v>
+        <v>30.434782608695</v>
       </c>
       <c r="L17" s="15">
-        <v>-4</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M17" s="15">
-        <v>140</v>
+        <v>172.727272727273</v>
       </c>
       <c r="N17" s="15">
-        <v>-31.428571428571</v>
+        <v>-31.818181818181</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-22.222222222222</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.105263157894</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.692307692307</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.940959409594</v>
+        <v>-95.283018867924</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.769230769230</v>
+        <v>120</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.956521739130</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J19" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K19" s="15">
-        <v>-35.593220338983</v>
+        <v>-23.4375</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.666666666666</v>
+        <v>-34.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-7.317073170731</v>
+        <v>4.255319148936</v>
       </c>
       <c r="N19" s="15">
-        <v>-74.496644295302</v>
+        <v>-72.471910112359</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-44.444444444444</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I20" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K20" s="15">
-        <v>-46.153846153846</v>
+        <v>-46.875</v>
       </c>
       <c r="L20" s="15">
-        <v>-48.148148148148</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.315789473684</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.857988165680</v>
+        <v>-95.760598503740</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>38.095238095238</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G21" s="17">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.747126436781</v>
+        <v>8.235294117647</v>
       </c>
       <c r="I21" s="17">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="J21" s="17">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.083969465648</v>
+        <v>-11.184210526315</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.911392405063</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.826086956521</v>
+        <v>5.46875</v>
       </c>
       <c r="N21" s="18">
-        <v>-88.427947598253</v>
+        <v>-87.476808905380</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1221,13 +1221,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>7</v>
@@ -1239,19 +1239,19 @@
         <v>75</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L23" s="15">
-        <v>-58.823529411764</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.25</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="F24" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G24" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.438356164383</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="J24" s="14">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.819819819819</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="L24" s="15">
-        <v>-27.642276422764</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.608695652173</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G25" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>-3.333333333333</v>
+        <v>2.941176470588</v>
       </c>
       <c r="I25" s="14">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J25" s="14">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.222222222222</v>
+        <v>-1.724137931034</v>
       </c>
       <c r="L25" s="15">
-        <v>4.761904761904</v>
+        <v>21.276595744680</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>18.518518518518</v>
+        <v>63.636363636363</v>
       </c>
       <c r="I26" s="14">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="J26" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K26" s="15">
-        <v>30</v>
+        <v>46.511627906976</v>
       </c>
       <c r="L26" s="15">
-        <v>30</v>
+        <v>31.25</v>
       </c>
       <c r="M26" s="15">
-        <v>23.809523809523</v>
+        <v>31.25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
+        <v>16</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15">
+        <v>166.666666666667</v>
+      </c>
+      <c r="I16" s="14">
+        <v>24</v>
+      </c>
+      <c r="J16" s="14">
         <v>14</v>
       </c>
-      <c r="G16" s="14">
-        <v>2</v>
-      </c>
-      <c r="H16" s="15">
-        <v>600</v>
-      </c>
-      <c r="I16" s="14">
-        <v>21</v>
-      </c>
-      <c r="J16" s="14">
-        <v>10</v>
-      </c>
       <c r="K16" s="15">
-        <v>110</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.258064516129</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M16" s="15">
-        <v>5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.558823529411</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,60 +978,60 @@
         <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>75</v>
+        <v>84.615384615384</v>
       </c>
       <c r="I17" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J17" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K17" s="15">
-        <v>30.434782608695</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.918918918918</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M17" s="15">
-        <v>172.727272727273</v>
+        <v>176.923076923077</v>
       </c>
       <c r="N17" s="15">
-        <v>-31.818181818181</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-20</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
         <v>15</v>
@@ -1043,13 +1043,13 @@
         <v>-28.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-25</v>
+        <v>-37.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-46.428571428571</v>
+        <v>-59.459459459459</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.283018867924</v>
+        <v>-95.923913043478</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.666666666666</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="I19" s="14">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="J19" s="14">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.4375</v>
+        <v>-19.480519480519</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.666666666666</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="M19" s="15">
-        <v>4.255319148936</v>
+        <v>8.771929824561</v>
       </c>
       <c r="N19" s="15">
-        <v>-72.471910112359</v>
+        <v>-69.902912621359</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-41.176470588235</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K20" s="15">
-        <v>-46.875</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="L20" s="15">
-        <v>-45.161290322580</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M20" s="15">
-        <v>-19.047619047619</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.760598503740</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>38.095238095238</v>
+        <v>-4</v>
       </c>
       <c r="F21" s="17">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>8.235294117647</v>
+        <v>16.279069767441</v>
       </c>
       <c r="I21" s="17">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="J21" s="17">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.184210526315</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.769230769230</v>
+        <v>-29.646017699115</v>
       </c>
       <c r="M21" s="18">
-        <v>5.46875</v>
+        <v>0</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.476808905380</v>
+        <v>-87.083671811535</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1233,25 +1233,25 @@
         <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L23" s="15">
-        <v>-60</v>
+        <v>-55</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.518518518518</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="F24" s="14">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G24" s="14">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.666666666666</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="I24" s="14">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J24" s="14">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.565217391304</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="L24" s="15">
-        <v>-17.777777777777</v>
+        <v>-21.710526315789</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.904761904761</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H25" s="15">
-        <v>2.941176470588</v>
+        <v>-3.125</v>
       </c>
       <c r="I25" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J25" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K25" s="15">
-        <v>-1.724137931034</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="L25" s="15">
-        <v>21.276595744680</v>
+        <v>3.508771929824</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>266.666666666667</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>63.636363636363</v>
+        <v>70.833333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K26" s="15">
-        <v>46.511627906976</v>
+        <v>46.153846153846</v>
       </c>
       <c r="L26" s="15">
-        <v>31.25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>31.25</v>
+        <v>35.714285714285</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-37.5</v>
+        <v>-60</v>
       </c>
       <c r="L28" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,79 +895,79 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>166.666666666667</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
         <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>71.428571428571</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.411764705882</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N16" s="15">
-        <v>-85</v>
+        <v>-86.813186813186</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>84.615384615384</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" s="15">
-        <v>38.461538461538</v>
+        <v>34.375</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.285714285714</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="M17" s="15">
-        <v>176.923076923077</v>
+        <v>186.666666666667</v>
       </c>
       <c r="N17" s="15">
-        <v>-20</v>
+        <v>-8.510638297872</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
+        <v>5</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.571428571428</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.5</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="M18" s="15">
-        <v>-59.459459459459</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.923913043478</v>
+        <v>-95.961995249406</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.651162790697</v>
+        <v>8.108108108108</v>
       </c>
       <c r="I19" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.480519480519</v>
+        <v>-16.867469879518</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.608695652173</v>
+        <v>-37.272727272727</v>
       </c>
       <c r="M19" s="15">
-        <v>8.771929824561</v>
+        <v>7.8125</v>
       </c>
       <c r="N19" s="15">
-        <v>-69.902912621359</v>
+        <v>-69.868995633187</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-53.333333333333</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K20" s="15">
-        <v>-51.351351351351</v>
+        <v>-51.219512195122</v>
       </c>
       <c r="L20" s="15">
-        <v>-45.454545454545</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-96</v>
+        <v>-96.116504854368</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-4</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="17">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>16.279069767441</v>
+        <v>10</v>
       </c>
       <c r="I21" s="17">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="J21" s="17">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.169491525423</v>
+        <v>-12.315270935960</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.646017699115</v>
+        <v>-31.007751937984</v>
       </c>
       <c r="M21" s="18">
-        <v>0</v>
+        <v>2.890173410404</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.083671811535</v>
+        <v>-87.249283667621</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
         <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I23" s="14">
+        <v>10</v>
+      </c>
+      <c r="J23" s="14">
         <v>9</v>
       </c>
-      <c r="J23" s="14">
-        <v>6</v>
-      </c>
       <c r="K23" s="15">
-        <v>50</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>-55</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-65.217391304347</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F24" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G24" s="14">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.090909090909</v>
+        <v>-27.173913043478</v>
       </c>
       <c r="I24" s="14">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="J24" s="14">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.086956521739</v>
+        <v>-24.598930481283</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.710526315789</v>
+        <v>-21.229050279329</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.047619047619</v>
+        <v>-16.568047337278</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G25" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H25" s="15">
-        <v>-3.125</v>
+        <v>2.702702702702</v>
       </c>
       <c r="I25" s="14">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="J25" s="14">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.838709677419</v>
+        <v>-5.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>3.508771929824</v>
+        <v>14.516129032258</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>44.444444444444</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>70.833333333333</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J26" s="14">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="K26" s="15">
-        <v>46.153846153846</v>
+        <v>17.142857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>33.333333333333</v>
+        <v>26.153846153846</v>
       </c>
       <c r="M26" s="15">
-        <v>35.714285714285</v>
+        <v>30.158730158730</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,11 +1428,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1551,26 +1551,26 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -920,27 +920,27 @@
         <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
         <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
         <v>12</v>
@@ -952,22 +952,22 @@
         <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>33.333333333333</v>
+        <v>47.368421052631</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.813186813186</v>
+        <v>-86.069651741293</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>66.666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K17" s="15">
-        <v>34.375</v>
+        <v>35.294117647058</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.510638297872</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M17" s="15">
-        <v>186.666666666667</v>
+        <v>187.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.510638297872</v>
+        <v>-13.207547169811</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-9.090909090909</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.615384615384</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.037037037037</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.536585365853</v>
+        <v>-50</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.961995249406</v>
+        <v>-95.164835164835</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F19" s="14">
         <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>8.108108108108</v>
+        <v>21.212121212121</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J19" s="14">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.867469879518</v>
+        <v>-14.130434782608</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.272727272727</v>
+        <v>-35.245901639344</v>
       </c>
       <c r="M19" s="15">
-        <v>7.8125</v>
+        <v>14.492753623188</v>
       </c>
       <c r="N19" s="15">
-        <v>-69.868995633187</v>
+        <v>-68.897637795275</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-47.058823529411</v>
+        <v>-37.5</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J20" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K20" s="15">
-        <v>-51.219512195122</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>-45.945945945945</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M20" s="15">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.116504854368</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>26</v>
+      </c>
+      <c r="D21" s="17">
         <v>18</v>
       </c>
-      <c r="D21" s="17">
-        <v>26</v>
-      </c>
       <c r="E21" s="18">
-        <v>-30.769230769230</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17">
         <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>10</v>
+        <v>7.777777777777</v>
       </c>
       <c r="I21" s="17">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.315270935960</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.007751937984</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="M21" s="18">
-        <v>2.890173410404</v>
+        <v>6.25</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.249283667621</v>
+        <v>-86.973180076628</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.173913043478</v>
+        <v>-26.041666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="J24" s="14">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.598930481283</v>
+        <v>-22.705314009661</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.229050279329</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="M24" s="15">
-        <v>-16.568047337278</v>
+        <v>-10.112359550561</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F25" s="14">
+        <v>33</v>
+      </c>
+      <c r="G25" s="14">
+        <v>39</v>
+      </c>
+      <c r="H25" s="15">
         <v>-15.384615384615</v>
       </c>
-      <c r="F25" s="14">
-        <v>38</v>
-      </c>
-      <c r="G25" s="14">
-        <v>37</v>
-      </c>
-      <c r="H25" s="15">
-        <v>2.702702702702</v>
-      </c>
       <c r="I25" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J25" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.333333333333</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>14.516129032258</v>
+        <v>-3.75</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-61.111111111111</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>5.555555555555</v>
+        <v>2.380952380952</v>
       </c>
       <c r="I26" s="14">
+        <v>95</v>
+      </c>
+      <c r="J26" s="14">
         <v>82</v>
       </c>
-      <c r="J26" s="14">
-        <v>70</v>
-      </c>
       <c r="K26" s="15">
-        <v>17.142857142857</v>
+        <v>15.853658536585</v>
       </c>
       <c r="L26" s="15">
-        <v>26.153846153846</v>
+        <v>28.378378378378</v>
       </c>
       <c r="M26" s="15">
-        <v>30.158730158730</v>
+        <v>26.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
@@ -1412,7 +1412,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>150</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14">
+        <v>6</v>
+      </c>
+      <c r="J15" s="14">
+        <v>5</v>
+      </c>
+      <c r="K15" s="15">
+        <v>20</v>
+      </c>
+      <c r="L15" s="15">
         <v>100</v>
       </c>
-      <c r="I15" s="14">
-        <v>5</v>
-      </c>
-      <c r="J15" s="14">
-        <v>3</v>
-      </c>
-      <c r="K15" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="L15" s="15">
-        <v>66.666666666666</v>
-      </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>47.368421052631</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.205128205128</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.5</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.069651741293</v>
+        <v>-85.253456221198</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>37.5</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I17" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J17" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K17" s="15">
-        <v>35.294117647058</v>
+        <v>19.512195121951</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.538461538461</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="M17" s="15">
-        <v>187.5</v>
+        <v>157.894736842105</v>
       </c>
       <c r="N17" s="15">
-        <v>-13.207547169811</v>
+        <v>-16.949152542372</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.666666666666</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>-29.032258064516</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.137931034482</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M18" s="15">
-        <v>-50</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.164835164835</v>
+        <v>-95.020746887966</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>11.111111111111</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>21.212121212121</v>
+        <v>11.627906976744</v>
       </c>
       <c r="I19" s="14">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="J19" s="14">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.130434782608</v>
+        <v>-8.411214953271</v>
       </c>
       <c r="L19" s="15">
-        <v>-35.245901639344</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M19" s="15">
-        <v>14.492753623188</v>
+        <v>25.641025641025</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.897637795275</v>
+        <v>-65.248226950354</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>300</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-37.5</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I20" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K20" s="15">
-        <v>-42.857142857142</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.461538461538</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="M20" s="15">
-        <v>-20</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N20" s="15">
-        <v>-96</v>
+        <v>-96.096096096096</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>44.444444444444</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="F21" s="17">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H21" s="18">
-        <v>7.777777777777</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="J21" s="17">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.692307692307</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.169014084507</v>
+        <v>-25.159235668789</v>
       </c>
       <c r="M21" s="18">
-        <v>6.25</v>
+        <v>10.849056603773</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.973180076628</v>
+        <v>-86.249268578115</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>200</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>21</v>
+        <v>133.333333333333</v>
+      </c>
+      <c r="M22" s="15">
+        <v>600</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
         <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L23" s="15">
-        <v>-45</v>
+        <v>-40</v>
       </c>
       <c r="M23" s="15">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.041666666666</v>
+        <v>-28.260869565217</v>
       </c>
       <c r="I24" s="14">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="J24" s="14">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.705314009661</v>
+        <v>-22.608695652173</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.568627450980</v>
+        <v>-19.457013574660</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.112359550561</v>
+        <v>-8.247422680412</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G25" s="14">
         <v>39</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.384615384615</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I25" s="14">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J25" s="14">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.333333333333</v>
+        <v>-10.309278350515</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.75</v>
+        <v>1.162790697674</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>8.333333333333</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F26" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H26" s="15">
-        <v>2.380952380952</v>
+        <v>-20</v>
       </c>
       <c r="I26" s="14">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J26" s="14">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K26" s="15">
-        <v>15.853658536585</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L26" s="15">
-        <v>28.378378378378</v>
+        <v>18.604651162790</v>
       </c>
       <c r="M26" s="15">
-        <v>26.666666666666</v>
+        <v>17.241379310344</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
         <v>5</v>
       </c>
-      <c r="J27" s="14">
-        <v>3</v>
-      </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,20 +1425,20 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>4</v>
-      </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
@@ -1447,10 +1447,10 @@
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L28" s="15">
         <v>-25</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-90</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,42 +1541,42 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.714285714285</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-91.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -926,7 +926,7 @@
         <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>9</v>
+      </c>
+      <c r="G16" s="14">
+        <v>11</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="I16" s="14">
+        <v>33</v>
+      </c>
+      <c r="J16" s="14">
         <v>25</v>
       </c>
-      <c r="F16" s="14">
-        <v>11</v>
-      </c>
-      <c r="G16" s="14">
-        <v>13</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-15.384615384615</v>
-      </c>
-      <c r="I16" s="14">
+      <c r="K16" s="15">
         <v>32</v>
       </c>
-      <c r="J16" s="14">
-        <v>23</v>
-      </c>
-      <c r="K16" s="15">
-        <v>39.130434782608</v>
-      </c>
       <c r="L16" s="15">
-        <v>-23.809523809523</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-3.030303030303</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.253456221198</v>
+        <v>-86.475409836065</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-57.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>5.555555555555</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I17" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J17" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K17" s="15">
-        <v>19.512195121951</v>
+        <v>18.75</v>
       </c>
       <c r="L17" s="15">
-        <v>-20.967741935483</v>
+        <v>-12.307692307692</v>
       </c>
       <c r="M17" s="15">
-        <v>157.894736842105</v>
+        <v>185</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.949152542372</v>
+        <v>-13.636363636363</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-71.428571428571</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-47.058823529411</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-36.842105263157</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.580645161290</v>
+        <v>6.451612903225</v>
       </c>
       <c r="M18" s="15">
-        <v>-48.936170212766</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.020746887966</v>
+        <v>-93.666026871401</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>13.333333333333</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>11.627906976744</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J19" s="14">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.411214953271</v>
+        <v>-6.722689075630</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.315789473684</v>
+        <v>-25</v>
       </c>
       <c r="M19" s="15">
-        <v>25.641025641025</v>
+        <v>35.365853658536</v>
       </c>
       <c r="N19" s="15">
-        <v>-65.248226950354</v>
+        <v>-63.606557377049</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-35.714285714285</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K20" s="15">
-        <v>-43.478260869565</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-39.534883720930</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.529411764705</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.096096096096</v>
+        <v>-96.164383561643</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.512820512820</v>
+        <v>13.793103448275</v>
       </c>
       <c r="F21" s="17">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G21" s="17">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.333333333333</v>
+        <v>-2.678571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="J21" s="17">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.615384615384</v>
+        <v>-7.266435986159</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.159235668789</v>
+        <v>-20.943952802359</v>
       </c>
       <c r="M21" s="18">
-        <v>10.849056603773</v>
+        <v>17.543859649122</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.249268578115</v>
+        <v>-85.668449197861</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>133.333333333333</v>
+        <v>40</v>
       </c>
       <c r="M22" s="15">
         <v>600</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I23" s="14">
         <v>12</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>-7.692307692307</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L23" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M23" s="15">
         <v>140</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.739130434782</v>
+        <v>-15</v>
       </c>
       <c r="F24" s="14">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.260869565217</v>
+        <v>-14.606741573033</v>
       </c>
       <c r="I24" s="14">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="J24" s="14">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.608695652173</v>
+        <v>-22</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.457013574660</v>
+        <v>-20.731707317073</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.247422680412</v>
+        <v>-10.550458715596</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.076923076923</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.076923076923</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="I25" s="14">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J25" s="14">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K25" s="15">
-        <v>-10.309278350515</v>
+        <v>-12.380952380952</v>
       </c>
       <c r="L25" s="15">
-        <v>1.162790697674</v>
+        <v>1.098901098901</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-45.454545454545</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>-20</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I26" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J26" s="14">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="K26" s="15">
-        <v>9.677419354838</v>
+        <v>7.766990291262</v>
       </c>
       <c r="L26" s="15">
-        <v>18.604651162790</v>
+        <v>19.354838709677</v>
       </c>
       <c r="M26" s="15">
-        <v>17.241379310344</v>
+        <v>13.265306122449</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1403,16 +1403,16 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,19 +1438,19 @@
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-45.454545454545</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L28" s="15">
         <v>-25</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,21 +1541,21 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,69 +905,69 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-18.181818181818</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="14">
         <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>32</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L16" s="15">
         <v>-26.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.333333333333</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.475409836065</v>
+        <v>-87.452471482889</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.545454545454</v>
+        <v>-10</v>
       </c>
       <c r="I17" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K17" s="15">
-        <v>18.75</v>
+        <v>17.307692307692</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.307692307692</v>
+        <v>-7.575757575757</v>
       </c>
       <c r="M17" s="15">
-        <v>185</v>
+        <v>154.166666666667</v>
       </c>
       <c r="N17" s="15">
-        <v>-13.636363636363</v>
+        <v>-15.277777777777</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.739130434782</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="L18" s="15">
-        <v>6.451612903225</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.888888888888</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.666026871401</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>8.333333333333</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>16.666666666666</v>
+        <v>25.531914893617</v>
       </c>
       <c r="I19" s="14">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="J19" s="14">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.722689075630</v>
+        <v>-2.307692307692</v>
       </c>
       <c r="L19" s="15">
-        <v>-25</v>
+        <v>-21.118012422360</v>
       </c>
       <c r="M19" s="15">
-        <v>35.365853658536</v>
+        <v>36.559139784946</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.606557377049</v>
+        <v>-63.817663817663</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="F20" s="14">
+        <v>13</v>
+      </c>
+      <c r="G20" s="14">
+        <v>13</v>
+      </c>
+      <c r="H20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
-        <v>10</v>
-      </c>
-      <c r="G20" s="14">
-        <v>11</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-9.090909090909</v>
-      </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J20" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K20" s="15">
-        <v>-41.666666666666</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.425531914893</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>-20</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.164383561643</v>
+        <v>-95.945945945946</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>13.793103448275</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.678571428571</v>
+        <v>7.079646017699</v>
       </c>
       <c r="I21" s="17">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="J21" s="17">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.266435986159</v>
+        <v>-5.696202531645</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.943952802359</v>
+        <v>-18.801089918256</v>
       </c>
       <c r="M21" s="18">
-        <v>17.543859649122</v>
+        <v>17.322834645669</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.668449197861</v>
+        <v>-85.548011639185</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-72.727272727272</v>
+        <v>-62.5</v>
       </c>
       <c r="I23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
         <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>-29.411764705882</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L23" s="15">
-        <v>-45.454545454545</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M23" s="15">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-15</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.606741573033</v>
+        <v>-19.540229885057</v>
       </c>
       <c r="I24" s="14">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="J24" s="14">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="K24" s="15">
-        <v>-22</v>
+        <v>-23.357664233576</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.731707317073</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.550458715596</v>
+        <v>-12.5</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-37.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H25" s="15">
-        <v>-25.581395348837</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="I25" s="14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J25" s="14">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.380952380952</v>
+        <v>-12.5</v>
       </c>
       <c r="L25" s="15">
-        <v>1.098901098901</v>
+        <v>-1.010101010101</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>-29.411764705882</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I26" s="14">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J26" s="14">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="K26" s="15">
-        <v>7.766990291262</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L26" s="15">
-        <v>19.354838709677</v>
+        <v>20</v>
       </c>
       <c r="M26" s="15">
-        <v>13.265306122449</v>
+        <v>16.504854368932</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-57.142857142857</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.307692307692</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>2</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
       <c r="J31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L31" s="15">
         <v>-91.666666666666</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>3</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>3</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>3</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-100</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -851,32 +851,32 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -902,45 +902,45 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N15" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>9</v>
@@ -952,22 +952,22 @@
         <v>-10</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>17.857142857142</v>
+        <v>24.137931034482</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.666666666666</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="M16" s="15">
-        <v>-13.157894736842</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.452471482889</v>
+        <v>-87.368421052631</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-10</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="I17" s="14">
+        <v>65</v>
+      </c>
+      <c r="J17" s="14">
         <v>61</v>
       </c>
-      <c r="J17" s="14">
-        <v>52</v>
-      </c>
       <c r="K17" s="15">
-        <v>17.307692307692</v>
+        <v>6.557377049180</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.575757575757</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M17" s="15">
-        <v>154.166666666667</v>
+        <v>140.740740740741</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.277777777777</v>
+        <v>-14.473684210526</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
+        <v>15</v>
+      </c>
+      <c r="G18" s="14">
         <v>19</v>
       </c>
-      <c r="G18" s="14">
-        <v>21</v>
-      </c>
       <c r="H18" s="15">
-        <v>-9.523809523809</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>-23.404255319148</v>
+        <v>-26</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.702702702702</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="M18" s="15">
-        <v>-36.842105263157</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.548387096774</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
         <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>45.454545454545</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F19" s="14">
         <v>59</v>
       </c>
       <c r="G19" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>25.531914893617</v>
+        <v>20.408163265306</v>
       </c>
       <c r="I19" s="14">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="J19" s="14">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.307692307692</v>
+        <v>-1.418439716312</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.118012422360</v>
+        <v>-17.261904761904</v>
       </c>
       <c r="M19" s="15">
-        <v>36.559139784946</v>
+        <v>43.298969072165</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.817663817663</v>
+        <v>-63.517060367454</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
         <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I20" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K20" s="15">
-        <v>-38.888888888888</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-42.622950819672</v>
       </c>
       <c r="M20" s="15">
-        <v>-19.512195121951</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.945945945946</v>
+        <v>-96.128318584070</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>11.111111111111</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F21" s="17">
+        <v>118</v>
+      </c>
+      <c r="G21" s="17">
         <v>121</v>
       </c>
-      <c r="G21" s="17">
-        <v>113</v>
-      </c>
       <c r="H21" s="18">
-        <v>7.079646017699</v>
+        <v>-2.479338842975</v>
       </c>
       <c r="I21" s="17">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="J21" s="17">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.696202531645</v>
+        <v>-6.140350877192</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.801089918256</v>
+        <v>-17.480719794344</v>
       </c>
       <c r="M21" s="18">
-        <v>17.322834645669</v>
+        <v>16.727272727272</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.548011639185</v>
+        <v>-85.682426404995</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>3</v>
-      </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-62.5</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.647058823529</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L23" s="15">
-        <v>-36.363636363636</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.5</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.540229885057</v>
+        <v>-26.744186046511</v>
       </c>
       <c r="I24" s="14">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="J24" s="14">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.357664233576</v>
+        <v>-23.890784982935</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.454545454545</v>
+        <v>-18.613138686131</v>
       </c>
       <c r="M24" s="15">
-        <v>-12.5</v>
+        <v>-13.899613899613</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.285714285714</v>
+        <v>75</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.027027027027</v>
+        <v>-12.5</v>
       </c>
       <c r="I25" s="14">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J25" s="14">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.5</v>
+        <v>-9.482758620689</v>
       </c>
       <c r="L25" s="15">
-        <v>-1.010101010101</v>
+        <v>3.960396039603</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-18.181818181818</v>
+        <v>-87.5</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.636363636363</v>
+        <v>-35</v>
       </c>
       <c r="I26" s="14">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J26" s="14">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K26" s="15">
-        <v>5.263157894736</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>20</v>
+        <v>17.307692307692</v>
       </c>
       <c r="M26" s="15">
-        <v>16.504854368932</v>
+        <v>5.172413793103</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I28" s="14">
+        <v>8</v>
+      </c>
+      <c r="J28" s="14">
+        <v>18</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L28" s="15">
         <v>0</v>
-      </c>
-      <c r="F28" s="14">
-        <v>4</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-20</v>
-      </c>
-      <c r="I28" s="14">
-        <v>7</v>
-      </c>
-      <c r="J28" s="14">
-        <v>15</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-53.333333333333</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>200</v>
       </c>
       <c r="L29" s="15">
         <v>200</v>
@@ -1507,32 +1507,32 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>200</v>
       </c>
       <c r="L30" s="15">
         <v>200</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>3</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>60</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="M15" s="15">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>-62.5</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K16" s="15">
-        <v>24.137931034482</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.404255319148</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-18.181818181818</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.368421052631</v>
+        <v>-88.410596026490</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-44.444444444444</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-29.629629629629</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
+        <v>69</v>
+      </c>
+      <c r="J17" s="14">
         <v>65</v>
       </c>
-      <c r="J17" s="14">
-        <v>61</v>
-      </c>
       <c r="K17" s="15">
-        <v>6.557377049180</v>
+        <v>6.153846153846</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.142857142857</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>140.740740740741</v>
+        <v>137.931034482759</v>
       </c>
       <c r="N17" s="15">
-        <v>-14.473684210526</v>
+        <v>-20.689655172413</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
+        <v>14</v>
+      </c>
+      <c r="G18" s="14">
         <v>15</v>
       </c>
-      <c r="G18" s="14">
-        <v>19</v>
-      </c>
       <c r="H18" s="15">
-        <v>-21.052631578947</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K18" s="15">
-        <v>-26</v>
+        <v>-28.301886792452</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.128205128205</v>
+        <v>-5</v>
       </c>
       <c r="M18" s="15">
-        <v>-40.322580645161</v>
+        <v>-40.625</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.75</v>
+        <v>-94.071762870514</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>20.408163265306</v>
+        <v>17.391304347826</v>
       </c>
       <c r="I19" s="14">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="J19" s="14">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.418439716312</v>
+        <v>-0.653594771241</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.261904761904</v>
+        <v>-16.483516483516</v>
       </c>
       <c r="M19" s="15">
-        <v>43.298969072165</v>
+        <v>42.056074766355</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.517060367454</v>
+        <v>-62.094763092269</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F20" s="14">
         <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-7.692307692307</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K20" s="15">
-        <v>-36.363636363636</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.622950819672</v>
+        <v>-42.1875</v>
       </c>
       <c r="M20" s="15">
-        <v>-20.454545454545</v>
+        <v>-24.489795918367</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.128318584070</v>
+        <v>-96.292585170340</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.692307692307</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="F21" s="17">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G21" s="17">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.479338842975</v>
+        <v>-4.504504504504</v>
       </c>
       <c r="I21" s="17">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J21" s="17">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.140350877192</v>
+        <v>-8.625336927223</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.480719794344</v>
+        <v>-17.518248175182</v>
       </c>
       <c r="M21" s="18">
-        <v>16.727272727272</v>
+        <v>14.915254237288</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.682426404995</v>
+        <v>-86.072308956450</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-71.428571428571</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-27.777777777777</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L23" s="15">
-        <v>-43.478260869565</v>
+        <v>-52</v>
       </c>
       <c r="M23" s="15">
-        <v>85.714285714285</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.578947368421</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.744186046511</v>
+        <v>-19.780219780219</v>
       </c>
       <c r="I24" s="14">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="J24" s="14">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.890784982935</v>
+        <v>-21.495327102803</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.613138686131</v>
+        <v>-14.864864864864</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.899613899613</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>75</v>
+        <v>-10</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.5</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I25" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J25" s="14">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.482758620689</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L25" s="15">
-        <v>3.960396039603</v>
+        <v>4.587155963302</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-87.5</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
         <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>-35</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="I26" s="14">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J26" s="14">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>-4.477611940298</v>
       </c>
       <c r="L26" s="15">
-        <v>17.307692307692</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>5.172413793103</v>
+        <v>2.4</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>80</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>3</v>
       </c>
-      <c r="E28" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F28" s="14">
-        <v>2</v>
-      </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
         <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.923076923076</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-70</v>
+        <v>-72.727272727272</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -926,21 +926,21 @@
         <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
@@ -952,22 +952,22 @@
         <v>-62.5</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>12.903225806451</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.083333333333</v>
+        <v>-28</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.410596026490</v>
+        <v>-88.535031847133</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I17" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J17" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K17" s="15">
-        <v>6.153846153846</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.166666666666</v>
+        <v>-1.298701298701</v>
       </c>
       <c r="M17" s="15">
-        <v>137.931034482759</v>
+        <v>153.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-20.689655172413</v>
+        <v>-16.483516483516</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-6.666666666666</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I18" s="14">
         <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.301886792452</v>
+        <v>-30.909090909090</v>
       </c>
       <c r="L18" s="15">
-        <v>-5</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-40.625</v>
+        <v>-43.283582089552</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.071762870514</v>
+        <v>-94.602272727272</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>8.333333333333</v>
+        <v>128.571428571429</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>17.391304347826</v>
+        <v>36.585365853658</v>
       </c>
       <c r="I19" s="14">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J19" s="14">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K19" s="15">
-        <v>-0.653594771241</v>
+        <v>4.375</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.483516483516</v>
+        <v>-15.228426395939</v>
       </c>
       <c r="M19" s="15">
-        <v>42.056074766355</v>
+        <v>42.735042735042</v>
       </c>
       <c r="N19" s="15">
-        <v>-62.094763092269</v>
+        <v>-61.342592592592</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="K20" s="15">
-        <v>-40.322580645161</v>
+        <v>-43.055555555555</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.1875</v>
+        <v>-40.579710144927</v>
       </c>
       <c r="M20" s="15">
-        <v>-24.489795918367</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.292585170340</v>
+        <v>-96.255707762557</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.586206896551</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.504504504504</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I21" s="17">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="J21" s="17">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.625336927223</v>
+        <v>-7.808564231738</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.518248175182</v>
+        <v>-17.194570135746</v>
       </c>
       <c r="M21" s="18">
-        <v>14.915254237288</v>
+        <v>16.560509554140</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.072308956450</v>
+        <v>-86.146858440575</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>600</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-36.842105263157</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L23" s="15">
-        <v>-52</v>
+        <v>-40</v>
       </c>
       <c r="M23" s="15">
-        <v>71.428571428571</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.571428571428</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="F24" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.780219780219</v>
+        <v>-18.085106382978</v>
       </c>
       <c r="I24" s="14">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="J24" s="14">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.495327102803</v>
+        <v>-20.639534883720</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.864864864864</v>
+        <v>-14.420062695924</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.695652173913</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-10</v>
+        <v>25</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G25" s="14">
         <v>29</v>
       </c>
       <c r="H25" s="15">
-        <v>-6.896551724137</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I25" s="14">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J25" s="14">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.523809523809</v>
+        <v>-7.462686567164</v>
       </c>
       <c r="L25" s="15">
-        <v>4.587155963302</v>
+        <v>6.896551724137</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>-36.585365853658</v>
+        <v>-25</v>
       </c>
       <c r="I26" s="14">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="J26" s="14">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.477611940298</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="L26" s="15">
-        <v>14.285714285714</v>
+        <v>16.129032258064</v>
       </c>
       <c r="M26" s="15">
-        <v>2.4</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-57.142857142857</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -860,14 +860,14 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -911,36 +911,36 @@
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N15" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
@@ -952,22 +952,22 @@
         <v>-62.5</v>
       </c>
       <c r="I16" s="14">
+        <v>37</v>
+      </c>
+      <c r="J16" s="14">
         <v>36</v>
       </c>
-      <c r="J16" s="14">
-        <v>33</v>
-      </c>
       <c r="K16" s="15">
-        <v>9.090909090909</v>
+        <v>2.777777777777</v>
       </c>
       <c r="L16" s="15">
-        <v>-28</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="M16" s="15">
-        <v>-20</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.535031847133</v>
+        <v>-88.509316770186</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="14">
         <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.636363636363</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I17" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J17" s="14">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K17" s="15">
-        <v>8.571428571428</v>
+        <v>1.282051282051</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.298701298701</v>
+        <v>-3.658536585365</v>
       </c>
       <c r="M17" s="15">
-        <v>153.333333333333</v>
+        <v>139.393939393939</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.483516483516</v>
+        <v>-19.387755102040</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-54.545454545454</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.909090909090</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.636363636363</v>
+        <v>-20</v>
       </c>
       <c r="M18" s="15">
-        <v>-43.283582089552</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.602272727272</v>
+        <v>-94.623655913978</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>128.571428571429</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>36.585365853658</v>
+        <v>42.5</v>
       </c>
       <c r="I19" s="14">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="J19" s="14">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="K19" s="15">
-        <v>4.375</v>
+        <v>7.647058823529</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.228426395939</v>
+        <v>-12.440191387559</v>
       </c>
       <c r="M19" s="15">
-        <v>42.735042735042</v>
+        <v>48.780487804878</v>
       </c>
       <c r="N19" s="15">
-        <v>-61.342592592592</v>
+        <v>-60.729613733905</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-41.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J20" s="14">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K20" s="15">
-        <v>-43.055555555555</v>
+        <v>-37.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.579710144927</v>
+        <v>-33.802816901408</v>
       </c>
       <c r="M20" s="15">
-        <v>-24.074074074074</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.255707762557</v>
+        <v>-96.003401360544</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,10 +1142,10 @@
         <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>7.692307692307</v>
+        <v>3.703703703703</v>
       </c>
       <c r="F21" s="17">
         <v>100</v>
@@ -1157,22 +1157,22 @@
         <v>-7.407407407407</v>
       </c>
       <c r="I21" s="17">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="J21" s="17">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.808564231738</v>
+        <v>-6.839622641509</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.194570135746</v>
+        <v>-15.598290598290</v>
       </c>
       <c r="M21" s="18">
-        <v>16.560509554140</v>
+        <v>18.618618618618</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.146858440575</v>
+        <v>-85.953058321479</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>600</v>
       </c>
       <c r="L22" s="15">
         <v>16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-21.052631578947</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L23" s="15">
-        <v>-40</v>
+        <v>-36</v>
       </c>
       <c r="M23" s="15">
-        <v>114.285714285714</v>
+        <v>128.571428571429</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-8.695652173913</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="F24" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.085106382978</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="J24" s="14">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="K24" s="15">
-        <v>-20.639534883720</v>
+        <v>-21.081081081081</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.420062695924</v>
+        <v>-14.117647058823</v>
       </c>
       <c r="M24" s="15">
-        <v>-7.142857142857</v>
+        <v>-6.410256410256</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G25" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>10.344827586206</v>
+        <v>22.580645161290</v>
       </c>
       <c r="I25" s="14">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="J25" s="14">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.462686567164</v>
+        <v>-4.195804195804</v>
       </c>
       <c r="L25" s="15">
-        <v>6.896551724137</v>
+        <v>7.03125</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>23.076923076923</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
         <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>-25</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I26" s="14">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J26" s="14">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.040816326530</v>
+        <v>-5.063291139240</v>
       </c>
       <c r="L26" s="15">
-        <v>16.129032258064</v>
+        <v>19.047619047619</v>
       </c>
       <c r="M26" s="15">
-        <v>5.882352941176</v>
+        <v>4.166666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L28" s="15">
         <v>20</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>2</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L31" s="15">
-        <v>-92.307692307692</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>3</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-62.5</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K16" s="15">
-        <v>2.777777777777</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.450980392156</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.276595744680</v>
+        <v>-18</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.509316770186</v>
+        <v>-87.761194029850</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.923076923076</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I17" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J17" s="14">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K17" s="15">
-        <v>1.282051282051</v>
+        <v>1.190476190476</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.658536585365</v>
+        <v>-2.298850574712</v>
       </c>
       <c r="M17" s="15">
-        <v>139.393939393939</v>
+        <v>150</v>
       </c>
       <c r="N17" s="15">
-        <v>-19.387755102040</v>
+        <v>-19.047619047619</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.636363636363</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.034482758620</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="L18" s="15">
-        <v>-20</v>
+        <v>-25.454545454545</v>
       </c>
       <c r="M18" s="15">
-        <v>-41.176470588235</v>
+        <v>-43.055555555555</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.623655913978</v>
+        <v>-94.716494845360</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>60</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>42.5</v>
+        <v>65.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J19" s="14">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="K19" s="15">
-        <v>7.647058823529</v>
+        <v>11.931818181818</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.440191387559</v>
+        <v>-10.454545454545</v>
       </c>
       <c r="M19" s="15">
-        <v>48.780487804878</v>
+        <v>57.6</v>
       </c>
       <c r="N19" s="15">
-        <v>-60.729613733905</v>
+        <v>-59.713701431492</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>-28.571428571428</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="I20" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J20" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K20" s="15">
-        <v>-37.333333333333</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.802816901408</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="M20" s="15">
-        <v>-22.950819672131</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.003401360544</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>27</v>
+      </c>
+      <c r="D21" s="17">
         <v>28</v>
       </c>
-      <c r="D21" s="17">
-        <v>27</v>
-      </c>
       <c r="E21" s="18">
-        <v>3.703703703703</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G21" s="17">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.407407407407</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="I21" s="17">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="J21" s="17">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.839622641509</v>
+        <v>-6.415929203539</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.598290598290</v>
+        <v>-15.230460921843</v>
       </c>
       <c r="M21" s="18">
-        <v>18.618618618618</v>
+        <v>22.608695652173</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.953058321479</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>600</v>
       </c>
       <c r="L22" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <v>250</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14">
         <v>4</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K23" s="15">
-        <v>-15.789473684210</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L23" s="15">
-        <v>-36</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="M23" s="15">
-        <v>128.571428571429</v>
+        <v>142.857142857143</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-26.923076923076</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.666666666666</v>
+        <v>-10.101010101010</v>
       </c>
       <c r="I24" s="14">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="J24" s="14">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.081081081081</v>
+        <v>-19.897959183673</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.117647058823</v>
+        <v>-12.290502793296</v>
       </c>
       <c r="M24" s="15">
-        <v>-6.410256410256</v>
+        <v>-8.187134502923</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F25" s="14">
         <v>38</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H25" s="15">
-        <v>22.580645161290</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="J25" s="14">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.195804195804</v>
+        <v>-6.493506493506</v>
       </c>
       <c r="L25" s="15">
-        <v>7.03125</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-45.454545454545</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H26" s="15">
-        <v>-31.818181818181</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I26" s="14">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="J26" s="14">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.063291139240</v>
+        <v>-5.357142857142</v>
       </c>
       <c r="L26" s="15">
-        <v>19.047619047619</v>
+        <v>13.571428571428</v>
       </c>
       <c r="M26" s="15">
-        <v>4.166666666666</v>
+        <v>8.163265306122</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-36.842105263157</v>
+        <v>-30</v>
       </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.571428571428</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1541,21 +1541,21 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-061pct.xlsx
+++ b/data/source/weekly/cs-en-us-061pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -914,16 +914,16 @@
         <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L15" s="15">
         <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
         <v>33.333333333333</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-20</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-58.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
         <v>41</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>2.439024390243</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.074074074074</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M16" s="15">
-        <v>-18</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.761194029850</v>
+        <v>-87.931034482758</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.043478260869</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I17" s="14">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J17" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K17" s="15">
-        <v>1.190476190476</v>
+        <v>-4.395604395604</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.298850574712</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>150</v>
+        <v>141.666666666667</v>
       </c>
       <c r="N17" s="15">
-        <v>-19.047619047619</v>
+        <v>-20.183486238532</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.870967741935</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.454545454545</v>
+        <v>-21.818181818181</v>
       </c>
       <c r="M18" s="15">
-        <v>-43.055555555555</v>
+        <v>-45.569620253164</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.716494845360</v>
+        <v>-94.756097560975</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>116.666666666667</v>
+        <v>280</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>65.714285714285</v>
+        <v>128.571428571429</v>
       </c>
       <c r="I19" s="14">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="J19" s="14">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K19" s="15">
-        <v>11.931818181818</v>
+        <v>19.889502762430</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.454545454545</v>
+        <v>-6.465517241379</v>
       </c>
       <c r="M19" s="15">
-        <v>57.6</v>
+        <v>60.740740740740</v>
       </c>
       <c r="N19" s="15">
-        <v>-59.713701431492</v>
+        <v>-58.587786259542</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>7</v>
-      </c>
       <c r="E20" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>-40.740740740740</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="I20" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J20" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K20" s="15">
-        <v>-39.024390243902</v>
+        <v>-40</v>
       </c>
       <c r="L20" s="15">
-        <v>-35.897435897435</v>
+        <v>-38.554216867469</v>
       </c>
       <c r="M20" s="15">
-        <v>-20.634920634920</v>
+        <v>-21.538461538461</v>
       </c>
       <c r="N20" s="15">
-        <v>-96</v>
+        <v>-96.118721461187</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.571428571428</v>
+        <v>19.047619047619</v>
       </c>
       <c r="F21" s="17">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G21" s="17">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.454545454545</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I21" s="17">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="J21" s="17">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.415929203539</v>
+        <v>-5.073995771670</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.230460921843</v>
+        <v>-14.149139579349</v>
       </c>
       <c r="M21" s="18">
-        <v>22.608695652173</v>
+        <v>21.351351351351</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.714285714285</v>
+        <v>-85.613585389298</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,7 +1207,7 @@
         <v>600</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M22" s="15">
         <v>250</v>
@@ -1220,23 +1220,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-66.666666666666</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>17</v>
@@ -1248,7 +1248,7 @@
         <v>-22.727272727272</v>
       </c>
       <c r="L23" s="15">
-        <v>-39.285714285714</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="M23" s="15">
         <v>142.857142857143</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>4.545454545454</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.101010101010</v>
+        <v>-4.819277108433</v>
       </c>
       <c r="I24" s="14">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="J24" s="14">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.897959183673</v>
+        <v>-18.811881188118</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.290502793296</v>
+        <v>-13.456464379947</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.187134502923</v>
+        <v>-8.379888268156</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G25" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I25" s="14">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J25" s="14">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.493506493506</v>
+        <v>-6.289308176100</v>
       </c>
       <c r="L25" s="15">
-        <v>5.882352941176</v>
+        <v>3.472222222222</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-10</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>-17.391304347826</v>
+        <v>2.439024390243</v>
       </c>
       <c r="I26" s="14">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="J26" s="14">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.357142857142</v>
+        <v>-3.428571428571</v>
       </c>
       <c r="L26" s="15">
-        <v>13.571428571428</v>
+        <v>9.740259740259</v>
       </c>
       <c r="M26" s="15">
-        <v>8.163265306122</v>
+        <v>10.457516339869</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1406,10 +1406,10 @@
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L27" s="15">
         <v>25</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
         <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-78.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>-71.428571428571</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L31" s="15">
-        <v>-84.615384615384</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1629,7 +1629,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33" s="15">
         <v>-100</v>
